--- a/shablonlar/1_talabalar.xlsx
+++ b/shablonlar/1_talabalar.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ma'lumot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ko'rsatma" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Ma'lumot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ko'rsatma" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -503,6 +503,7 @@
     <col width="30" customWidth="1" min="10" max="10"/>
     <col width="25" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="44" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -566,6 +567,11 @@
           <t>Kurs koordinatori telefoni</t>
         </is>
       </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Yashash manzili</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -626,6 +632,11 @@
       <c r="L2" s="4" t="inlineStr">
         <is>
           <t>+998 71 000 00 00</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>Toshkent shahri, Yunusobod tumani, Amir Temur ko‘chasi, 1-uy</t>
         </is>
       </c>
     </row>
@@ -640,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -659,7 +670,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>1. HEMIS → «Talabalar kontingenti» eksport faylini to'g'ridan-to'g'ri yuborish mumkin: pasport, manzil va boshqa ustunlar e'tiborsiz qoldiriladi, ikki qatorli sarlavha ham tushuniladi.</t>
+          <t>1. HEMIS → «Talabalar kontingenti» eksport faylini to'g'ridan-to'g'ri yuborish mumkin: pasport va boshqa keraksiz ustunlar e'tiborsiz qoldiriladi (yashash manzili o'qiladi — ota-onaga xat uchun), ikki qatorli sarlavha ham tushuniladi.</t>
         </is>
       </c>
     </row>
@@ -974,6 +985,28 @@
       <c r="D20" s="8" t="inlineStr">
         <is>
           <t>+998 71 000 00 00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Yashash manzili</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>yo'q</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Ota-onaga ogohlantirish xati uchun («Chora ko'rish»). HEMIS'dagi «Viloyat», «Tuman», «Manzil» ustunlari alohida bo'lsa ham o'qiladi va birlashtiriladi. Bo'sh bo'lsa — xat tayyorlashda qo'lda kiritiladi</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Toshkent shahri, Yunusobod tumani, Amir Temur ko‘chasi, 1-uy</t>
         </is>
       </c>
     </row>
